--- a/docs/REPAIR01_20260823/02 · القيادة.xlsx
+++ b/docs/REPAIR01_20260823/02 · القيادة.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>لوحة القيادة — Deputy Executive Dashboard</t>
+          <t>لوحة النائب</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -25471,7 +25471,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 01 من 12 · [الرؤية بالنطاق] · لوحة القيادة — Deputy Executive Dashboard</t>
+          <t>■ الشاشة 01 من 12 · [الرؤية بالنطاق] · لوحة النائب</t>
         </is>
       </c>
       <c r="B23" s="2" t="n"/>
@@ -26130,7 +26130,7 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>02 من 12 — ما قبلها: لوحة القيادة — Deputy Executive Dashboard · ما بعدها: التقرير اليومي — Deputy Daily Report</t>
+          <t>02 من 12 — ما قبلها: لوحة النائب · ما بعدها: التقرير اليومي للنائب</t>
         </is>
       </c>
       <c r="D39" s="2" t="n"/>
@@ -26724,7 +26724,7 @@
     <row r="52" ht="20" customHeight="1">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 03 من 12 · [التقارير الدورية] · التقرير اليومي — Deputy Daily Report</t>
+          <t>■ الشاشة 03 من 12 · [التقارير الدورية] · التقرير اليومي للنائب</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
@@ -26804,7 +26804,7 @@
       <c r="B54" s="3" t="n"/>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>03 من 12 — ما قبلها: الإدارات — نطاقي والشركة · ما بعدها: التقرير الأسبوعي — Deputy Weekly Performance Review</t>
+          <t>03 من 12 — ما قبلها: الإدارات — نطاقي والشركة · ما بعدها: مراجعة الأداء الأسبوعية</t>
         </is>
       </c>
       <c r="D54" s="2" t="n"/>
@@ -27493,7 +27493,7 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 04 من 12 · [التقارير الدورية] · التقرير الأسبوعي — Deputy Weekly Performance Review</t>
+          <t>■ الشاشة 04 من 12 · [التقارير الدورية] · مراجعة الأداء الأسبوعية</t>
         </is>
       </c>
       <c r="B65" s="2" t="n"/>
@@ -27573,7 +27573,7 @@
       <c r="B67" s="3" t="n"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>04 من 12 — ما قبلها: التقرير اليومي — Deputy Daily Report · ما بعدها: التقرير الشهري — Deputy Monthly Review</t>
+          <t>04 من 12 — ما قبلها: التقرير اليومي للنائب · ما بعدها: المراجعة الشهرية للنائب</t>
         </is>
       </c>
       <c r="D67" s="2" t="n"/>
@@ -28037,7 +28037,7 @@
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 05 من 12 · [التقارير الدورية] · التقرير الشهري — Deputy Monthly Review</t>
+          <t>■ الشاشة 05 من 12 · [التقارير الدورية] · المراجعة الشهرية للنائب</t>
         </is>
       </c>
       <c r="B78" s="2" t="n"/>
@@ -28117,7 +28117,7 @@
       <c r="B80" s="3" t="n"/>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>05 من 12 — ما قبلها: التقرير الأسبوعي — Deputy Weekly Performance Review · ما بعدها: صندوق الاعتمادات — Unified Deputy Approval Inbox</t>
+          <t>05 من 12 — ما قبلها: مراجعة الأداء الأسبوعية · ما بعدها: صندوق اعتمادات النائب</t>
         </is>
       </c>
       <c r="D80" s="2" t="n"/>
@@ -28651,7 +28651,7 @@
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 06 من 12 · [صناديق القرار] · صندوق الاعتمادات — Unified Deputy Approval Inbox</t>
+          <t>■ الشاشة 06 من 12 · [صناديق القرار] · صندوق اعتمادات النائب</t>
         </is>
       </c>
       <c r="B93" s="2" t="n"/>
@@ -28731,7 +28731,7 @@
       <c r="B95" s="3" t="n"/>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>06 من 12 — ما قبلها: التقرير الشهري — Deputy Monthly Review · ما بعدها: الاعتمادات المالية حسب الصلاحية</t>
+          <t>06 من 12 — ما قبلها: المراجعة الشهرية للنائب · ما بعدها: الاعتمادات المالية حسب الصلاحية</t>
         </is>
       </c>
       <c r="D95" s="2" t="n"/>
@@ -29415,7 +29415,7 @@
       <c r="B109" s="3" t="n"/>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>07 من 12 — ما قبلها: صندوق الاعتمادات — Unified Deputy Approval Inbox · ما بعدها: الاستثناءات والخطوط الحمراء ضمن صلاحيتي</t>
+          <t>07 من 12 — ما قبلها: صندوق اعتمادات النائب · ما بعدها: الاستثناءات والخطوط الحمراء ضمن صلاحيتي</t>
         </is>
       </c>
       <c r="D109" s="2" t="n"/>
@@ -30114,7 +30114,7 @@
       <c r="B123" s="3" t="n"/>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>08 من 12 — ما قبلها: الاعتمادات المالية حسب الصلاحية · ما بعدها: التصعيدات — Escalations within Scope</t>
+          <t>08 من 12 — ما قبلها: الاعتمادات المالية حسب الصلاحية · ما بعدها: التصعيدات داخل النطاق</t>
         </is>
       </c>
       <c r="D123" s="2" t="n"/>
@@ -30688,7 +30688,7 @@
     <row r="135" ht="20" customHeight="1">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 09 من 12 · [صناديق القرار] · التصعيدات — Escalations within Scope</t>
+          <t>■ الشاشة 09 من 12 · [صناديق القرار] · التصعيدات داخل النطاق</t>
         </is>
       </c>
       <c r="B135" s="2" t="n"/>
@@ -31427,7 +31427,7 @@
       <c r="B152" s="3" t="n"/>
       <c r="C152" s="9" t="inlineStr">
         <is>
-          <t>10 من 12 — ما قبلها: التصعيدات — Escalations within Scope · ما بعدها: متابعة القرارات — Deputy Actions Follow-up</t>
+          <t>10 من 12 — ما قبلها: التصعيدات داخل النطاق · ما بعدها: متابعة قرارات النائب</t>
         </is>
       </c>
       <c r="D152" s="2" t="n"/>
@@ -31846,7 +31846,7 @@
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>■ الشاشة 11 من 12 · [المتابعة] · متابعة القرارات — Deputy Actions Follow-up</t>
+          <t>■ الشاشة 11 من 12 · [المتابعة] · متابعة قرارات النائب</t>
         </is>
       </c>
       <c r="B163" s="2" t="n"/>
@@ -32470,7 +32470,7 @@
       <c r="B178" s="3" t="n"/>
       <c r="C178" s="9" t="inlineStr">
         <is>
-          <t>12 من 12 — ما قبلها: متابعة القرارات — Deputy Actions Follow-up · ما بعدها: نهاية الدورة</t>
+          <t>12 من 12 — ما قبلها: متابعة قرارات النائب · ما بعدها: نهاية الدورة</t>
         </is>
       </c>
       <c r="D178" s="2" t="n"/>
@@ -34997,7 +34997,7 @@
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>لوحة القيادة — Deputy Executive Dashboard</t>
+          <t>لوحة النائب</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>التقرير اليومي — Deputy Daily Report</t>
+          <t>التقرير اليومي للنائب</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -35201,7 +35201,7 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>التقرير الأسبوعي — Deputy Weekly Performance Review</t>
+          <t>مراجعة الأداء الأسبوعية</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -35269,7 +35269,7 @@
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>التقرير الشهري — Deputy Monthly Review</t>
+          <t>المراجعة الشهرية للنائب</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -35337,7 +35337,7 @@
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>صندوق الاعتمادات — Unified Deputy Approval Inbox</t>
+          <t>صندوق اعتمادات النائب</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -35541,7 +35541,7 @@
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>التصعيدات — Escalations within Scope</t>
+          <t>التصعيدات داخل النطاق</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -35677,7 +35677,7 @@
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>متابعة القرارات — Deputy Actions Follow-up</t>
+          <t>متابعة قرارات النائب</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
